--- a/simulations/AO_hydrogen_peroxide_real/economics_AO_real.xlsx
+++ b/simulations/AO_hydrogen_peroxide_real/economics_AO_real.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AO_hydrogen_peroxide_real\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6DD8FC-8EF5-4A51-8709-FC4E1491608F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B452819-24A7-46B4-A3C8-CD316F323993}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -1221,7 +1221,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1346,6 +1346,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1367,9 +1370,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1843,16 +1844,16 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="58"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="59"/>
       <c r="L13" s="33" t="s">
         <v>89</v>
       </c>
@@ -2056,16 +2057,16 @@
       <c r="T16" s="47"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="59"/>
       <c r="L17" s="33" t="s">
         <v>137</v>
       </c>
@@ -2181,16 +2182,16 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="58"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="59"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -2567,16 +2568,16 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="61"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="62"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2635,16 +2636,16 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="59"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
@@ -2703,16 +2704,16 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="58"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="59"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
@@ -3006,11 +3007,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="62">
+      <c r="A3" s="63">
         <v>2022</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
@@ -3024,11 +3025,11 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -3067,19 +3068,19 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="56"/>
-      <c r="B9" s="58"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="17">
         <f>SUM(C6:C8)</f>
         <v>7.3406250000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
@@ -3094,19 +3095,19 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
       <c r="C12" s="29">
         <f>C11</f>
         <v>1.2302313863938941</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="58"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -3133,19 +3134,19 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="62"/>
-      <c r="B16" s="62"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="63"/>
       <c r="C16" s="29">
         <f>SUM(C14:C15)</f>
         <v>6.6372571860307392</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
@@ -3160,18 +3161,18 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
+      <c r="A19" s="63"/>
+      <c r="B19" s="63"/>
       <c r="C19" s="17">
         <f>C18</f>
         <v>0.67170633697106619</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="58"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="17">
         <f>C9+C12+C16+C19</f>
         <v>15.8798199093957</v>
@@ -3241,13 +3242,13 @@
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
       <c r="I4" s="54" t="s">
         <v>143</v>
       </c>
@@ -3256,8 +3257,12 @@
         <v>1846.5517241379312</v>
       </c>
       <c r="K4" s="42">
-        <f>J4*596.2/550.8*596.2/550.8*596.2/550.8</f>
-        <v>2341.8312530358171</v>
+        <f>J4*596.2/550.8*596.2/550.8*596.2/550.8/(1+0.02)^30</f>
+        <v>1292.8568617044248</v>
+      </c>
+      <c r="L4" s="64">
+        <f>K4/1000</f>
+        <v>1.2928568617044247</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
@@ -3277,7 +3282,7 @@
         <f>D5*E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="63">
+      <c r="G5" s="56">
         <f>F5/Summary!$C$23</f>
         <v>0</v>
       </c>
@@ -3309,7 +3314,7 @@
         <f>D6*E6</f>
         <v>4559.8286518044033</v>
       </c>
-      <c r="G6" s="63">
+      <c r="G6" s="56">
         <f>F6/Summary!$C$23</f>
         <v>0.1216075914903002</v>
       </c>
@@ -3334,7 +3339,7 @@
         <f>D7*E7</f>
         <v>15334.818709681698</v>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="56">
         <f>F7/Summary!$C$23</f>
         <v>0.40896939591948012</v>
       </c>
@@ -3358,25 +3363,25 @@
         <f>D8*E8</f>
         <v>54643.13673198496</v>
       </c>
-      <c r="G8" s="63">
+      <c r="G8" s="56">
         <f>F8/Summary!$C$23</f>
         <v>1.4572960426533341</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="63">
         <v>2022</v>
       </c>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="63"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="56"/>
       <c r="I9" s="54" t="s">
         <v>147</v>
       </c>
@@ -3406,7 +3411,7 @@
         <f>D10*E10</f>
         <v>53.596851855470291</v>
       </c>
-      <c r="G10" s="63">
+      <c r="G10" s="56">
         <f>F10/Summary!$C$23</f>
         <v>1.4293923222371456E-3</v>
       </c>
@@ -3447,7 +3452,7 @@
         <f>D11*E11</f>
         <v>519.27944536163693</v>
       </c>
-      <c r="G11" s="63">
+      <c r="G11" s="56">
         <f>F11/Summary!$C$23</f>
         <v>1.3848836761850409E-2</v>
       </c>
@@ -3482,7 +3487,7 @@
         <f>D12*E12</f>
         <v>310.31859510331162</v>
       </c>
-      <c r="G12" s="63">
+      <c r="G12" s="56">
         <f>F12/Summary!$C$23</f>
         <v>8.2759901362157908E-3</v>
       </c>
@@ -3500,11 +3505,11 @@
         <f>(F5+F6+F8+F10+F11+F12)/1000000*8000</f>
         <v>480.68928220887824</v>
       </c>
-      <c r="I13" s="62">
+      <c r="I13" s="63">
         <v>2050</v>
       </c>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
       <c r="U13" s="15"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
@@ -3540,11 +3545,15 @@
         <v>145</v>
       </c>
       <c r="J15" s="42">
-        <f>J10*596.2/550.8*596.2/550.8*596.2/550.8</f>
-        <v>1914.3541195451519</v>
+        <f>J10*596.2/550.8*596.2/550.8*596.2/550.8/(1+0.02)^30</f>
+        <v>1056.8591805996487</v>
       </c>
       <c r="K15" s="42">
         <v>2400</v>
+      </c>
+      <c r="L15" s="64">
+        <f>J15/1000</f>
+        <v>1.0568591805996486</v>
       </c>
       <c r="T15" s="15"/>
       <c r="U15" s="15"/>
@@ -3559,11 +3568,15 @@
         <v>146</v>
       </c>
       <c r="J16" s="42">
-        <f>J11*596.2/550.8*596.2/550.8*596.2/550.8</f>
-        <v>4014.5678623471154</v>
+        <f>J11*596.2/550.8*596.2/550.8*596.2/550.8/(1+0.02)^30</f>
+        <v>2216.3260486361569</v>
       </c>
       <c r="K16" s="42">
         <v>4600</v>
+      </c>
+      <c r="L16" s="64">
+        <f>J16/1000</f>
+        <v>2.2163260486361569</v>
       </c>
       <c r="T16" s="15"/>
       <c r="U16" s="15"/>
@@ -3629,14 +3642,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="C2" s="63"/>
+      <c r="E2" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="62"/>
+      <c r="F2" s="63"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
